--- a/漢字（かんじ）/k.xlsx
+++ b/漢字（かんじ）/k.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="か" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="551">
   <si>
     <t>仮名</t>
   </si>
@@ -1685,6 +1685,12 @@
 条件｜じょうけん</t>
   </si>
   <si>
+    <t>倹</t>
+  </si>
+  <si>
+    <t>倹約｜けんやく</t>
+  </si>
+  <si>
     <t>検</t>
   </si>
   <si>
@@ -2200,7 +2206,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2243,13 +2249,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -2712,28 +2711,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2742,118 +2744,115 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4998,7 +4997,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="30.6666666666667" customWidth="1"/>
@@ -5343,70 +5342,81 @@
         <v>419</v>
       </c>
     </row>
-    <row r="26" ht="54" spans="1:3">
-      <c r="A26" s="1" t="s">
+    <row r="26" ht="18" spans="1:3">
+      <c r="A26" t="s">
         <v>405</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>420</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="27" ht="18" spans="1:3">
+    <row r="27" ht="54" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>405</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="28" ht="54" spans="1:3">
+    <row r="28" ht="18" spans="1:3">
       <c r="A28" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="29" ht="18" spans="1:3">
+    <row r="29" ht="54" spans="1:3">
       <c r="A29" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="30" ht="31.2" spans="1:3">
+    <row r="30" ht="18" spans="1:3">
       <c r="A30" s="1" t="s">
         <v>405</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="31" ht="36" spans="1:3">
+    <row r="31" ht="31.2" spans="1:3">
       <c r="A31" s="1" t="s">
         <v>405</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="8" t="s">
         <v>431</v>
+      </c>
+    </row>
+    <row r="32" ht="36" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -5447,619 +5457,619 @@
     </row>
     <row r="2" ht="36" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" ht="64.2" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" ht="88.8" customHeight="1" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" ht="72" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" ht="57.6" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" ht="20.4" customHeight="1" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" ht="20.4" customHeight="1" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" ht="20.4" customHeight="1" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="12" ht="20.4" customHeight="1" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" ht="20.4" customHeight="1" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" ht="20.4" customHeight="1" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16" ht="20.4" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="19" ht="144" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>325</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" ht="37.8" customHeight="1" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="21" ht="54" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" ht="54" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" ht="54" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="24" ht="36" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C25" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="27" ht="27.6" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" ht="72" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" ht="36" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="31" ht="54" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="32" ht="36" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="33" ht="36" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="35" ht="54" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="36" ht="72" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="37" ht="126" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" ht="55.2" customHeight="1" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="40" ht="34.2" customHeight="1" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="42" ht="39.6" customHeight="1" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:3">
       <c r="A44" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="47" ht="90" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="51" ht="54" spans="1:3">
       <c r="A51" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="52" ht="36" spans="1:3">
       <c r="A52" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:3">
       <c r="A53" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/k.xlsx
+++ b/漢字（かんじ）/k.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="か" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="556">
   <si>
     <t>仮名</t>
   </si>
@@ -792,6 +792,16 @@
     <t>鐘</t>
   </si>
   <si>
+    <t>かど</t>
+  </si>
+  <si>
+    <t>角</t>
+  </si>
+  <si>
+    <t>街角｜まちかど
+海角｜うみかど</t>
+  </si>
+  <si>
     <t>き</t>
   </si>
   <si>
@@ -814,7 +824,10 @@
 借金｜しゃっきん
 金曜日｜きんようび
 現金｜げんきん
-金額｜きんがく</t>
+金額｜きんがく
+賞金｜しょうきん
+資金｜しきん
+住宅資金｜じゅうたくしきん</t>
   </si>
   <si>
     <t>記</t>
@@ -853,7 +866,8 @@
   <si>
     <t>最近｜さいきん
 接近｜せっきん
-近況｜きんきょう</t>
+近況｜きんきょう
+近似｜きんじ</t>
   </si>
   <si>
     <t>期</t>
@@ -874,6 +888,7 @@
     <t>通勤｜つうきん
 欠勤｜けっきん
 出勤｜しゅっきん
+常勤｜じょうきん
 勤労｜きんろう
 勤勉｜きんべん
 勤務｜きんむ
@@ -906,7 +921,10 @@
     <t>客</t>
   </si>
   <si>
-    <t>顧客｜こきゃく</t>
+    <t>顧客｜こきゃく
+観客｜かんきゃく
+客席｜きゃくせき
+観客席｜かんきゃくせき</t>
   </si>
   <si>
     <t>貴</t>
@@ -950,7 +968,8 @@
     <t>曲</t>
   </si>
   <si>
-    <t>歌曲｜かきょく
+    <t>曲線｜きょくせん
+歌曲｜かきょく
 楽曲｜がっきょく
 応援曲｜おうえんきょく</t>
   </si>
@@ -1253,7 +1272,8 @@
   <si>
     <t>請求｜せいきゅう
 要求｜ようきゅう
-求職｜きゅうしょく</t>
+求職｜きゅうしょく
+求婚｜きゅうこん</t>
   </si>
   <si>
     <t>給</t>
@@ -1504,10 +1524,10 @@
 人傑｜じんけつ</t>
   </si>
   <si>
-    <t>警</t>
-  </si>
-  <si>
-    <t>警察｜けいさ</t>
+    <t>刑</t>
+  </si>
+  <si>
+    <t>刑事｜けいじ</t>
   </si>
   <si>
     <t>欠</t>
@@ -1519,16 +1539,22 @@
 欠席｜けっせき</t>
   </si>
   <si>
+    <t>警</t>
+  </si>
+  <si>
+    <t>警察｜けいさ</t>
+  </si>
+  <si>
+    <t>穴</t>
+  </si>
+  <si>
+    <t>洞穴｜どうけつ</t>
+  </si>
+  <si>
     <t>携</t>
   </si>
   <si>
     <t>携帯｜けいたい</t>
-  </si>
-  <si>
-    <t>穴</t>
-  </si>
-  <si>
-    <t>洞穴｜どうけつ</t>
   </si>
   <si>
     <t>形</t>
@@ -1617,25 +1643,8 @@
     <t>権</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <charset val="128"/>
-      </rPr>
-      <t>権利｜けんり（权利）
+    <t>権利｜けんり
 権限｜けんげん</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（权限）</t>
-    </r>
   </si>
   <si>
     <t>健</t>
@@ -2013,7 +2022,8 @@
     <t>効</t>
   </si>
   <si>
-    <t>効果｜こうか
+    <t>有効｜ゆうこう
+効果｜こうか
 効能｜こうのう
 抑制効果｜よくせいこうか
 促進効果｜そくしんこうか</t>
@@ -2110,7 +2120,8 @@
   <si>
     <t>好評｜こうひょう
 好評発売中｜こうひょうはつば
-友好｜ゆうこう</t>
+友好｜ゆうこう
+格好｜かっこう</t>
   </si>
   <si>
     <t>巧</t>
@@ -2178,7 +2189,8 @@
     <t>婚</t>
   </si>
   <si>
-    <t>結婚｜けっこん
+    <t>求婚｜きゅうこん
+結婚｜けっこん
 離婚｜りこん
 離婚調停｜りこんちょうてい</t>
   </si>
@@ -3197,7 +3209,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -4113,6 +4125,17 @@
       </c>
       <c r="F46" s="1" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="47" ht="36" spans="1:7">
+      <c r="E47" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -4159,652 +4182,652 @@
     </row>
     <row r="2" ht="70.8" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" ht="72" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" ht="144" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" ht="89.4" customHeight="1" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" ht="54" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" ht="72" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="B7" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="8" ht="36" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" ht="90" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="10" ht="54" spans="1:7">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="10" ht="72" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" ht="144" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" ht="36" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" ht="36" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" ht="36" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" ht="54" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" ht="36" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" ht="90" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" ht="36" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" ht="72" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" ht="36" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" ht="36" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" ht="72" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" ht="72" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" ht="36" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" ht="72" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" ht="54" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" ht="54" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" ht="54" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" ht="72" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" ht="36" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" ht="126" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="47" ht="54" spans="1:3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="47" ht="72" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="49" ht="90" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -4837,155 +4860,155 @@
     </row>
     <row r="2" ht="54" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" ht="57.6" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" ht="18.6" customHeight="1" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" ht="18.6" customHeight="1" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" ht="18.6" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" ht="37.8" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" ht="36" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -4997,7 +5020,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="30.6666666666667" customWidth="1"/>
@@ -5026,397 +5049,408 @@
     </row>
     <row r="2" ht="49.2" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" ht="73.8" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" ht="90" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
+      </c>
+      <c r="B6" t="s">
+        <v>378</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="8" ht="69" spans="1:7">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="8" ht="18" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="9" ht="36" spans="1:7">
+        <v>386</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="9" ht="69" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="10" ht="18" spans="1:7">
+        <v>388</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="10" ht="36" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="11" ht="36" spans="1:7">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="11" ht="18" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="12" ht="90" spans="1:7">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" ht="36" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="13" ht="54" spans="1:7">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="13" ht="90" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="14" ht="18" spans="1:7">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="14" ht="54" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" ht="54" spans="1:3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="18" ht="18" spans="1:3">
+        <v>404</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" ht="54" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>403</v>
+        <v>369</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="19" ht="36" spans="1:3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>406</v>
+        <v>369</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>408</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="20" ht="35.4" customHeight="1" spans="1:3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="20" ht="36" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="21" ht="54" spans="1:3">
+        <v>411</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="21" ht="35.4" customHeight="1" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="22" ht="54" spans="1:3">
+      <c r="A22" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1" spans="1:3">
-      <c r="A22" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="B22" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="23" ht="22.2" customHeight="1" spans="1:3">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="24" ht="54" spans="1:3">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="24" ht="22.2" customHeight="1" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="25" ht="36" spans="1:3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="25" ht="54" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="26" ht="18" spans="1:3">
-      <c r="A26" t="s">
-        <v>405</v>
-      </c>
-      <c r="B26" t="s">
-        <v>420</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="27" ht="54" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B27" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C27" s="2" t="s">
+    </row>
+    <row r="26" ht="36" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="28" ht="18" spans="1:3">
+      <c r="C26" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="27" ht="18" spans="1:3">
+      <c r="A27" t="s">
+        <v>410</v>
+      </c>
+      <c r="B27" t="s">
+        <v>425</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="28" ht="54" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="29" ht="54" spans="1:3">
+        <v>427</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="30" ht="18" spans="1:3">
+        <v>410</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="30" ht="54" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="31" ht="31.2" spans="1:3">
+        <v>410</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="31" ht="18" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="32" ht="36" spans="1:3">
+        <v>433</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="32" ht="31.2" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="33" ht="36" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -5457,619 +5491,619 @@
     </row>
     <row r="2" ht="36" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" ht="64.2" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" ht="88.8" customHeight="1" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" ht="72" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" ht="57.6" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" ht="20.4" customHeight="1" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" ht="20.4" customHeight="1" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" ht="20.4" customHeight="1" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" ht="20.4" customHeight="1" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="14" ht="20.4" customHeight="1" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="15" ht="20.4" customHeight="1" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" ht="20.4" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" ht="144" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" ht="37.8" customHeight="1" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" ht="54" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22" ht="54" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" ht="54" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" ht="36" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C25" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" ht="27.6" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="28" ht="72" spans="1:3">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="28" ht="90" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="30" ht="36" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="31" ht="54" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="32" ht="36" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="33" ht="36" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" ht="54" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" ht="72" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="37" ht="126" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="5" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="39" ht="55.2" customHeight="1" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="40" ht="34.2" customHeight="1" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1" spans="1:3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="41" ht="72" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="42" ht="39.6" customHeight="1" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:3">
       <c r="A44" s="5" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="47" ht="90" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="51" ht="72" spans="1:3">
+      <c r="A51" s="1" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="51" ht="54" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="B51" s="1" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="52" ht="36" spans="1:3">
       <c r="A52" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:3">
       <c r="A53" s="1" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/k.xlsx
+++ b/漢字（かんじ）/k.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="か" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="562">
   <si>
     <t>仮名</t>
   </si>
@@ -683,7 +683,8 @@
 間隔｜かんかく
 民間｜みんかん
 時間｜じかん
-空間｜くうかん</t>
+空間｜くうかん
+中間｜ちゅうかん</t>
   </si>
   <si>
     <t>かみ</t>
@@ -1002,13 +1003,13 @@
 奇跡｜きせき</t>
   </si>
   <si>
-    <t>きずな</t>
-  </si>
-  <si>
-    <t>絆</t>
-  </si>
-  <si>
-    <t>強い絆｜つよいきずな</t>
+    <t>きし</t>
+  </si>
+  <si>
+    <t>岸</t>
+  </si>
+  <si>
+    <t>岸辺｜きしへん</t>
   </si>
   <si>
     <t>軌</t>
@@ -1018,10 +1019,13 @@
 軌跡｜きせき</t>
   </si>
   <si>
-    <t>きし</t>
-  </si>
-  <si>
-    <t>岸</t>
+    <t>きつ</t>
+  </si>
+  <si>
+    <t>喫</t>
+  </si>
+  <si>
+    <t>喫煙室｜きつえんしつ</t>
   </si>
   <si>
     <t>揮</t>
@@ -1031,13 +1035,13 @@
 揮発｜きはつ</t>
   </si>
   <si>
-    <t>きつ</t>
-  </si>
-  <si>
-    <t>喫</t>
-  </si>
-  <si>
-    <t>喫煙室｜きつえんしつ</t>
+    <t>きず</t>
+  </si>
+  <si>
+    <t>傷</t>
+  </si>
+  <si>
+    <t>傷口｜きずぐち</t>
   </si>
   <si>
     <t>起</t>
@@ -1046,6 +1050,15 @@
     <t>喚起｜かんき
 起点｜きてん
 起動｜きどう</t>
+  </si>
+  <si>
+    <t>きずな</t>
+  </si>
+  <si>
+    <t>絆</t>
+  </si>
+  <si>
+    <t>強い絆｜つよいきずな</t>
   </si>
   <si>
     <t>季</t>
@@ -1650,7 +1663,8 @@
     <t>健</t>
   </si>
   <si>
-    <t>健康｜けんこう</t>
+    <t>健康｜けんこう
+健闘｜けんとう</t>
   </si>
   <si>
     <t>験</t>
@@ -1665,7 +1679,8 @@
   </si>
   <si>
     <t>保険｜ほけん
-危険｜きけん</t>
+危険｜きけん
+冒険｜ぼうけん</t>
   </si>
   <si>
     <t>見</t>
@@ -1769,6 +1784,18 @@
 小型｜こがた</t>
   </si>
   <si>
+    <t>事</t>
+  </si>
+  <si>
+    <t>事柄｜ことがら</t>
+  </si>
+  <si>
+    <t>子</t>
+  </si>
+  <si>
+    <t>親子｜おやこ</t>
+  </si>
+  <si>
     <t>こく</t>
   </si>
   <si>
@@ -1779,10 +1806,10 @@
 国際｜こくさい</t>
   </si>
   <si>
-    <t>子</t>
-  </si>
-  <si>
-    <t>親子｜おやこ</t>
+    <t>戸</t>
+  </si>
+  <si>
+    <t>江戸｜えど</t>
   </si>
   <si>
     <t>告</t>
@@ -1822,10 +1849,10 @@
     </r>
   </si>
   <si>
-    <t>戸</t>
-  </si>
-  <si>
-    <t>江戸｜えど</t>
+    <t>古</t>
+  </si>
+  <si>
+    <t>古典｜こてん</t>
   </si>
   <si>
     <t>刻</t>
@@ -1837,12 +1864,6 @@
 深刻｜しんこく</t>
   </si>
   <si>
-    <t>古</t>
-  </si>
-  <si>
-    <t>古典｜こてん</t>
-  </si>
-  <si>
     <t>固</t>
   </si>
   <si>
@@ -1850,19 +1871,16 @@
 確固｜かっこ</t>
   </si>
   <si>
+    <t>雇</t>
+  </si>
+  <si>
+    <t>雇用｜こよう</t>
+  </si>
+  <si>
     <t>こえ</t>
   </si>
   <si>
     <t>声</t>
-  </si>
-  <si>
-    <t>雇</t>
-  </si>
-  <si>
-    <t>雇用｜こよう</t>
-  </si>
-  <si>
-    <t>超え</t>
   </si>
   <si>
     <t>顧</t>
@@ -1870,6 +1888,9 @@
   <si>
     <t>顧問｜こもん
 顧客｜こきゃく</t>
+  </si>
+  <si>
+    <t>超え</t>
   </si>
   <si>
     <t>庫</t>
@@ -3953,7 +3974,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="38" ht="108" spans="1:7">
+    <row r="38" ht="126" spans="1:7">
       <c r="A38" s="1" t="s">
         <v>97</v>
       </c>
@@ -4416,25 +4437,28 @@
       <c r="F13" s="1" t="s">
         <v>245</v>
       </c>
+      <c r="G13" s="1" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="14" ht="36" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>193</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" ht="54" spans="1:7">
@@ -4442,10 +4466,19 @@
         <v>193</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="16" ht="36" spans="1:7">
@@ -4453,10 +4486,10 @@
         <v>193</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4464,10 +4497,10 @@
         <v>193</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:3">
@@ -4475,10 +4508,10 @@
         <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
@@ -4486,10 +4519,10 @@
         <v>193</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" ht="90" spans="1:3">
@@ -4497,10 +4530,10 @@
         <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" ht="36" spans="1:3">
@@ -4508,10 +4541,10 @@
         <v>193</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4519,315 +4552,315 @@
         <v>193</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" ht="72" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" ht="36" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" ht="36" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" ht="72" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" ht="72" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" ht="36" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" ht="72" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" ht="54" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" ht="54" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" ht="54" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" ht="72" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="44" ht="36" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" ht="126" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" ht="72" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" ht="90" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -4860,155 +4893,155 @@
     </row>
     <row r="2" ht="54" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" ht="57.6" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" ht="18.6" customHeight="1" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" ht="18.6" customHeight="1" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" ht="18.6" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" ht="37.8" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" ht="36" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -5049,408 +5082,408 @@
     </row>
     <row r="2" ht="49.2" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" ht="73.8" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" ht="90" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B6" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" ht="69" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" ht="36" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" ht="36" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" ht="90" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" ht="54" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" ht="54" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" ht="36" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" ht="35.4" customHeight="1" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="22" ht="54" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" ht="22.2" customHeight="1" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="26" ht="36" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B27" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" ht="54" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" ht="54" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" ht="31.2" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" ht="36" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -5491,619 +5524,628 @@
     </row>
     <row r="2" ht="36" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" ht="64.2" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E3" t="s">
         <v>446</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>449</v>
+      <c r="F3" t="s">
+        <v>451</v>
+      </c>
+      <c r="G3" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="4" ht="88.8" customHeight="1" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="5" ht="72" spans="1:7">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="5" ht="108" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="6" ht="18" spans="1:7">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="6" ht="72" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" ht="57.6" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" ht="20.4" customHeight="1" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="10" ht="20.4" customHeight="1" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" ht="20.4" customHeight="1" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" ht="20.4" customHeight="1" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" ht="20.4" customHeight="1" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" ht="20.4" customHeight="1" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" ht="20.4" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" ht="144" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" ht="37.8" customHeight="1" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" ht="54" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" ht="54" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="23" ht="54" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="24" ht="36" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C25" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" ht="27.6" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" ht="90" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" ht="36" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
     </row>
     <row r="31" ht="54" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
     </row>
     <row r="32" ht="36" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="33" ht="36" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
     <row r="35" ht="54" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="36" ht="72" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="37" ht="126" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="5" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="39" ht="55.2" customHeight="1" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="40" ht="34.2" customHeight="1" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="41" ht="72" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="42" ht="39.6" customHeight="1" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:3">
       <c r="A44" s="5" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="47" ht="90" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="51" ht="72" spans="1:3">
       <c r="A51" s="1" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="52" ht="36" spans="1:3">
       <c r="A52" s="1" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:3">
       <c r="A53" s="1" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/k.xlsx
+++ b/漢字（かんじ）/k.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="か" sheetId="1" r:id="rId1"/>
@@ -436,7 +436,8 @@
   </si>
   <si>
     <t>全快｜ぜんかい
-快楽｜かいらく</t>
+快楽｜かいらく
+快晴｜かいせい</t>
   </si>
   <si>
     <t>荷</t>
@@ -1155,7 +1156,8 @@
   </si>
   <si>
     <t>協会｜きょうかい
-協力｜きょうりょく</t>
+協力｜きょうりょく
+協調｜きょうちょう</t>
   </si>
   <si>
     <t>京</t>
@@ -1212,7 +1214,8 @@
   <si>
     <t>強力｜きょうりょく
 強化｜きょうか
-補強｜ほきょう</t>
+補強｜ほきょう
+強調｜きょうちょう</t>
   </si>
   <si>
     <t>郷</t>
@@ -2046,6 +2049,7 @@
     <t>有効｜ゆうこう
 効果｜こうか
 効能｜こうのう
+効力｜こうりょく
 抑制効果｜よくせいこうか
 促進効果｜そくしんこうか</t>
   </si>
@@ -2053,7 +2057,8 @@
     <t>功</t>
   </si>
   <si>
-    <t>成功｜せいこう</t>
+    <t>成功｜せいこう
+功績｜こうせき</t>
   </si>
   <si>
     <t>攻</t>
@@ -2155,7 +2160,8 @@
     <t>幸</t>
   </si>
   <si>
-    <t>幸福の科学｜こうふくのかがく</t>
+    <t>幸福｜こうふく
+幸運｜こううん</t>
   </si>
   <si>
     <t>口</t>
@@ -2204,7 +2210,8 @@
     <t>混</t>
   </si>
   <si>
-    <t>混雑｜こんざつ</t>
+    <t>混雑｜こんざつ
+混合｜こんごう</t>
   </si>
   <si>
     <t>婚</t>
@@ -2431,14 +2438,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2889,7 +2896,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2900,6 +2907,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3664,7 +3674,7 @@
       <c r="B22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="10" t="s">
         <v>87</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -3677,14 +3687,14 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" ht="36" spans="1:7">
+    <row r="23" ht="54" spans="1:7">
       <c r="A23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -3704,7 +3714,7 @@
       <c r="B24" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>94</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -4613,7 +4623,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="28" ht="36" spans="1:3">
+    <row r="28" ht="54" spans="1:3">
       <c r="A28" s="1" t="s">
         <v>280</v>
       </c>
@@ -4701,7 +4711,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="36" ht="54" spans="1:3">
+    <row r="36" ht="72" spans="1:3">
       <c r="A36" s="1" t="s">
         <v>280</v>
       </c>
@@ -5325,7 +5335,7 @@
       <c r="A19" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>412</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -5446,7 +5456,7 @@
       <c r="A30" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="8" t="s">
         <v>435</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -5471,7 +5481,7 @@
       <c r="B32" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="9" t="s">
         <v>440</v>
       </c>
     </row>
@@ -5865,7 +5875,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="28" ht="90" spans="1:3">
+    <row r="28" ht="108" spans="1:3">
       <c r="A28" s="1" t="s">
         <v>493</v>
       </c>
@@ -5876,7 +5886,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="29" ht="18" spans="1:3">
+    <row r="29" ht="36" spans="1:3">
       <c r="A29" s="1" t="s">
         <v>493</v>
       </c>
@@ -6030,14 +6040,14 @@
         <v>539</v>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1" spans="1:3">
+    <row r="43" ht="36" spans="1:3">
       <c r="A43" s="1" t="s">
         <v>493</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="6" t="s">
         <v>541</v>
       </c>
     </row>
@@ -6107,14 +6117,14 @@
         <v>553</v>
       </c>
     </row>
-    <row r="50" ht="18" spans="1:3">
+    <row r="50" ht="36" spans="1:3">
       <c r="A50" s="1" t="s">
         <v>550</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>555</v>
       </c>
     </row>

--- a/漢字（かんじ）/k.xlsx
+++ b/漢字（かんじ）/k.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="か" sheetId="1" r:id="rId1"/>
@@ -425,7 +425,8 @@
     <t>海</t>
   </si>
   <si>
-    <t>海外｜かいがい</t>
+    <t>海外｜かいがい
+海抜｜かいばつ</t>
   </si>
   <si>
     <t>許可｜きょか
@@ -1644,7 +1645,8 @@
   <si>
     <t>掲示｜けいじ
 掲示板｜けいじばん
-掲示物｜けいじぶつ</t>
+掲示物｜けいじぶつ
+掲載｜けいさい</t>
   </si>
   <si>
     <t>茎</t>
@@ -2005,8 +2007,9 @@
   </si>
   <si>
     <t>高等｜こうとう
+高度｜こうど
 高級｜こうき
-高層｜こうそう</t>
+高層｜こうそう　</t>
   </si>
   <si>
     <t>校</t>
@@ -2438,14 +2441,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2907,15 +2910,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3674,7 +3677,7 @@
       <c r="B22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -3683,7 +3686,7 @@
       <c r="F22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="10" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3694,7 +3697,7 @@
       <c r="B23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -5320,7 +5323,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="18" ht="54" spans="1:3">
+    <row r="18" ht="72" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>373</v>
       </c>
@@ -5335,7 +5338,7 @@
       <c r="A19" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>412</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -5456,7 +5459,7 @@
       <c r="A30" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>435</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -5481,7 +5484,7 @@
       <c r="B32" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>440</v>
       </c>
     </row>
@@ -5809,7 +5812,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="22" ht="54" spans="1:3">
+    <row r="22" ht="72" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>493</v>
       </c>
@@ -6047,7 +6050,7 @@
       <c r="B43" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="2" t="s">
         <v>541</v>
       </c>
     </row>

--- a/漢字（かんじ）/k.xlsx
+++ b/漢字（かんじ）/k.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="か" sheetId="1" r:id="rId1"/>
@@ -1073,7 +1073,8 @@
     <t>希</t>
   </si>
   <si>
-    <t>希望｜きぼう</t>
+    <t>希望｜きぼう
+希薄｜きはく</t>
   </si>
   <si>
     <t>企</t>
@@ -1188,7 +1189,8 @@
     <t>状況｜じょうきょう
 近況｜きんきょう
 近況報告｜きんきょうほうこく
-不況｜ふきょう</t>
+不況｜ふきょう
+好況｜こうきょう</t>
   </si>
   <si>
     <t>教育｜きょういく</t>
@@ -1992,7 +1994,9 @@
     <t>公務員｜こうむいん
 主人公｜しゅじんこう
 公共｜こうきょう
-公職｝こうしょく</t>
+公職｜こうしょく
+公表｜こうひょう
+公式｜こうしき</t>
   </si>
   <si>
     <t>交</t>
@@ -2148,7 +2152,8 @@
   </si>
   <si>
     <t>好評｜こうひょう
-好評発売中｜こうひょうはつば
+好評発売中｜こうひょうはつばいちゅう
+好況｜こうきょう
 友好｜ゆうこう
 格好｜かっこう</t>
   </si>
@@ -2899,7 +2904,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2916,9 +2921,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3686,7 +3688,7 @@
       <c r="F22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="2" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3717,7 +3719,7 @@
       <c r="B24" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>94</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -4505,7 +4507,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" ht="36" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>193</v>
       </c>
@@ -4670,7 +4672,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="32" ht="72" spans="1:3">
+    <row r="32" ht="90" spans="1:3">
       <c r="A32" s="1" t="s">
         <v>280</v>
       </c>
@@ -5511,7 +5513,7 @@
   <dimension ref="A1:G53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="31.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="39.3333333333333" customWidth="1"/>
     <col min="7" max="7" width="33.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6021,7 +6023,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="41" ht="72" spans="1:3">
+    <row r="41" ht="108" spans="1:3">
       <c r="A41" s="1" t="s">
         <v>493</v>
       </c>
